--- a/academias/Laboratorio Clínico - Estadisticos 20211.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20211.xlsx
@@ -554,13 +554,13 @@
         <v>22.86</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -872,10 +872,10 @@
         <v>6.6</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -904,13 +904,13 @@
         <v>2.94</v>
       </c>
       <c r="I13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -976,22 +976,25 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>69.23</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>30.77</v>
+      </c>
+      <c r="I2">
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1008,22 +1011,25 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>11.43</v>
+      </c>
+      <c r="I3">
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1040,22 +1046,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>32.26</v>
+      </c>
+      <c r="I4">
+        <v>8.1</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1072,22 +1081,25 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>76.47</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>23.53</v>
+      </c>
+      <c r="I5">
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1104,22 +1116,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1136,22 +1151,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1168,22 +1186,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I8">
+        <v>8.800000000000001</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1200,22 +1221,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>11.43</v>
+      </c>
+      <c r="I9">
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1232,22 +1256,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>97.06</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>2.94</v>
+      </c>
+      <c r="I10">
+        <v>9.4</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1264,22 +1291,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>74.36</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>25.64</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1296,22 +1326,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>57.14</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>42.86</v>
+      </c>
+      <c r="I12">
+        <v>7.2</v>
       </c>
       <c r="J12">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1328,22 +1361,25 @@
         <v>34</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>97.06</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>2.94</v>
+      </c>
+      <c r="I13">
+        <v>8.1</v>
       </c>
       <c r="J13">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1409,19 +1445,19 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>74.36</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="H2">
-        <v>25.64</v>
+        <v>20.51</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1444,25 +1480,25 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>77.14</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H3">
-        <v>22.86</v>
+        <v>11.43</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1479,19 +1515,19 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4">
-        <v>70.97</v>
+        <v>74.19</v>
       </c>
       <c r="H4">
-        <v>29.03</v>
+        <v>25.81</v>
       </c>
       <c r="I4">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1514,19 +1550,19 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>76.47</v>
+        <v>79.41</v>
       </c>
       <c r="H5">
-        <v>23.53</v>
+        <v>20.59</v>
       </c>
       <c r="I5">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1561,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1631,7 +1667,7 @@
         <v>20</v>
       </c>
       <c r="I8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1654,19 +1690,19 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>91.43000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H9">
-        <v>8.57</v>
+        <v>11.43</v>
       </c>
       <c r="I9">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1689,19 +1725,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>91.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H10">
-        <v>8.82</v>
+        <v>2.94</v>
       </c>
       <c r="I10">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1724,16 +1760,16 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>84.62</v>
+        <v>74.36</v>
       </c>
       <c r="H11">
-        <v>15.38</v>
+        <v>25.64</v>
       </c>
       <c r="I11">
         <v>7.2</v>
@@ -1759,25 +1795,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>62.86</v>
+        <v>60</v>
       </c>
       <c r="H12">
-        <v>37.14</v>
+        <v>40</v>
       </c>
       <c r="I12">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1806,13 +1842,13 @@
         <v>2.94</v>
       </c>
       <c r="I13">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Laboratorio Clínico - Estadisticos 20211.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -100,6 +100,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -152,8 +156,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -454,42 +460,45 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -512,19 +521,19 @@
       <c r="F2">
         <v>10</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>74.36</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>25.64</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7.5</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -547,19 +556,19 @@
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>77.14</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>22.86</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>7.3</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -582,19 +591,19 @@
       <c r="F4">
         <v>9</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>70.97</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>29.03</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -617,19 +626,19 @@
       <c r="F5">
         <v>8</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>76.47</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>23.53</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.3</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -652,19 +661,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>100</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>7.7</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -687,19 +696,19 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>100</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
         <v>8.6</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -722,19 +731,19 @@
       <c r="F8">
         <v>7</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>80</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>20</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.5</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -757,19 +766,19 @@
       <c r="F9">
         <v>3</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>91.43000000000001</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>8.57</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>8.9</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -792,19 +801,19 @@
       <c r="F10">
         <v>3</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>91.18000000000001</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>8.82</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -827,19 +836,19 @@
       <c r="F11">
         <v>6</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>84.62</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>15.38</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -862,19 +871,19 @@
       <c r="F12">
         <v>13</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>62.86</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>37.14</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -897,19 +906,19 @@
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>97.06</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>2.94</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>9</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
@@ -923,42 +932,45 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -981,19 +993,19 @@
       <c r="F2">
         <v>12</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>69.23</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>30.77</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7.9</v>
       </c>
       <c r="J2">
         <v>8</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>20.51</v>
       </c>
     </row>
@@ -1016,19 +1028,19 @@
       <c r="F3">
         <v>4</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>88.56999999999999</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>11.43</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>7.6</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1051,19 +1063,19 @@
       <c r="F4">
         <v>10</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>67.73999999999999</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>32.26</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>8.1</v>
       </c>
       <c r="J4">
         <v>10</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>32.26</v>
       </c>
     </row>
@@ -1086,19 +1098,19 @@
       <c r="F5">
         <v>8</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>76.47</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>23.53</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>8</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>23.53</v>
       </c>
     </row>
@@ -1121,19 +1133,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>100</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1156,19 +1168,19 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>100</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1191,19 +1203,19 @@
       <c r="F8">
         <v>7</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>80</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>20</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1226,19 +1238,19 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>88.56999999999999</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>11.43</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1261,19 +1273,19 @@
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>97.06</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>2.94</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>9.4</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1296,19 +1308,19 @@
       <c r="F11">
         <v>10</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>74.36</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>25.64</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1331,19 +1343,19 @@
       <c r="F12">
         <v>15</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>57.14</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>42.86</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.2</v>
       </c>
       <c r="J12">
         <v>6</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>17.14</v>
       </c>
     </row>
@@ -1366,19 +1378,19 @@
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>97.06</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>2.94</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>8.1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1392,42 +1404,45 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1450,19 +1465,19 @@
       <c r="F2">
         <v>8</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>79.48999999999999</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>20.51</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1485,19 +1500,19 @@
       <c r="F3">
         <v>4</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>88.56999999999999</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>11.43</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>7.6</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1520,19 +1535,19 @@
       <c r="F4">
         <v>8</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>74.19</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>25.81</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.2</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1555,19 +1570,19 @@
       <c r="F5">
         <v>7</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>79.41</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>20.59</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1590,19 +1605,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>100</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>7.8</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1625,19 +1640,19 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>100</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
         <v>8.6</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1660,19 +1675,19 @@
       <c r="F8">
         <v>7</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>80</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>20</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1695,19 +1710,19 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>88.56999999999999</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>11.43</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1730,19 +1745,19 @@
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>97.06</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>2.94</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1765,19 +1780,19 @@
       <c r="F11">
         <v>10</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>74.36</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>25.64</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1800,19 +1815,19 @@
       <c r="F12">
         <v>14</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>60</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>40</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1835,19 +1850,19 @@
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>97.06</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>2.94</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Laboratorio Clínico - Estadisticos 20211.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20211.xlsx
@@ -101,7 +101,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Laboratorio Clínico - Estadisticos 20211.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20211.xlsx
@@ -988,25 +988,25 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>69.23</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>30.77</v>
+        <v>12.82</v>
       </c>
       <c r="I2" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>20.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1058,25 +1058,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>67.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="H4" s="1">
-        <v>32.26</v>
+        <v>25.81</v>
       </c>
       <c r="I4" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>32.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1093,25 +1093,25 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>76.47</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>23.53</v>
+        <v>8.82</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>23.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1338,25 +1338,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G12" s="1">
-        <v>57.14</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>42.86</v>
+        <v>34.29</v>
       </c>
       <c r="I12" s="2">
         <v>7.2</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>17.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1460,19 +1460,19 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>79.48999999999999</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>20.51</v>
+        <v>10.26</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1495,19 +1495,19 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>88.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="H3" s="1">
-        <v>11.43</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1530,19 +1530,19 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>74.19</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>25.81</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1565,19 +1565,19 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>79.41</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>20.59</v>
+        <v>8.82</v>
       </c>
       <c r="I5" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1670,16 +1670,16 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>80</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>20</v>
+        <v>5.71</v>
       </c>
       <c r="I8" s="2">
         <v>8.800000000000001</v>
@@ -1705,19 +1705,19 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>88.56999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>11.43</v>
+        <v>5.71</v>
       </c>
       <c r="I9" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         <v>2.94</v>
       </c>
       <c r="I10" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H11" s="1">
-        <v>25.64</v>
+        <v>15.38</v>
       </c>
       <c r="I11" s="2">
         <v>7.2</v>
@@ -1810,19 +1810,19 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>60</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>40</v>
+        <v>25.71</v>
       </c>
       <c r="I12" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>2.94</v>
       </c>
       <c r="I13" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
         <v>0</v>
